--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_OV_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>186905</v>
       </c>
       <c r="C2">
-        <v>270692</v>
+        <v>271086</v>
       </c>
       <c r="D2">
-        <v>316616</v>
+        <v>316816</v>
       </c>
       <c r="E2">
-        <v>341686</v>
+        <v>341743</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -405,13 +405,13 @@
         <v>225589</v>
       </c>
       <c r="C3">
-        <v>324105</v>
+        <v>324718</v>
       </c>
       <c r="D3">
-        <v>374223</v>
+        <v>374391</v>
       </c>
       <c r="E3">
-        <v>406075</v>
+        <v>406125</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -422,13 +422,13 @@
         <v>201837</v>
       </c>
       <c r="C4">
-        <v>300183</v>
+        <v>300723</v>
       </c>
       <c r="D4">
-        <v>354764</v>
+        <v>354982</v>
       </c>
       <c r="E4">
-        <v>387876</v>
+        <v>387919</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -442,7 +442,7 @@
         <v>219824</v>
       </c>
       <c r="D5">
-        <v>246941</v>
+        <v>246943</v>
       </c>
       <c r="E5">
         <v>269836</v>
@@ -456,7 +456,7 @@
         <v>136799</v>
       </c>
       <c r="C6">
-        <v>192871</v>
+        <v>192872</v>
       </c>
       <c r="D6">
         <v>218723</v>
@@ -490,13 +490,13 @@
         <v>705791</v>
       </c>
       <c r="C8">
-        <v>1030532</v>
+        <v>1039920</v>
       </c>
       <c r="D8">
-        <v>1228322</v>
+        <v>1236082</v>
       </c>
       <c r="E8">
-        <v>1334288</v>
+        <v>1335453</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>199575</v>
       </c>
       <c r="C9">
-        <v>280517</v>
+        <v>280702</v>
       </c>
       <c r="D9">
-        <v>318552</v>
+        <v>318588</v>
       </c>
       <c r="E9">
-        <v>344321</v>
+        <v>344328</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>85714</v>
       </c>
       <c r="C10">
-        <v>117483</v>
+        <v>117496</v>
       </c>
       <c r="D10">
-        <v>134894</v>
+        <v>134910</v>
       </c>
       <c r="E10">
-        <v>143119</v>
+        <v>143130</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>15753</v>
+        <v>15759</v>
       </c>
       <c r="C11">
-        <v>20502</v>
+        <v>20508</v>
       </c>
       <c r="D11">
-        <v>23275</v>
+        <v>23279</v>
       </c>
       <c r="E11">
-        <v>26644</v>
+        <v>26647</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>37561</v>
+        <v>37570</v>
       </c>
       <c r="C12">
-        <v>53791</v>
+        <v>53798</v>
       </c>
       <c r="D12">
-        <v>61466</v>
+        <v>61468</v>
       </c>
       <c r="E12">
-        <v>64367</v>
+        <v>64368</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>48170</v>
       </c>
       <c r="C13">
-        <v>65450</v>
+        <v>65454</v>
       </c>
       <c r="D13">
-        <v>75874</v>
+        <v>75882</v>
       </c>
       <c r="E13">
-        <v>81447</v>
+        <v>81453</v>
       </c>
     </row>
   </sheetData>
